--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2018_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2018_atacama.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:45</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,10 +672,10 @@
         <v>0.2</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -715,13 +715,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="11">
@@ -738,10 +738,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.38</v>
